--- a/input/images/tables/provenance-elements.xlsx
+++ b/input/images/tables/provenance-elements.xlsx
@@ -418,7 +418,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>﻿Is_New</t>
+          <t>Is_New</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
